--- a/backtest_results.xlsx
+++ b/backtest_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Configuration" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuration" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -452,13 +452,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -470,7 +470,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -581,32 +581,32 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>45919</v>
+        <v>45754</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Multi Day Breakout</t>
+          <t>Extended Gap Down</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>246.3</v>
+        <v>223.78</v>
       </c>
       <c r="E2" t="n">
-        <v>240.21</v>
+        <v>261</v>
       </c>
       <c r="F2" t="n">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>-1000.3</v>
+        <v>-967.98</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.48</v>
+        <v>-16.64</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -617,33 +617,234 @@
         <v>1000</v>
       </c>
       <c r="K2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L2" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Float: 50.0M</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>163.74</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Volume ratio: 2.3x</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>86294601892</v>
       </c>
       <c r="S2" t="b">
         <v>0</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Extended Gap Down</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>298.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>321.67</v>
+      </c>
+      <c r="F3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-835.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.78</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="n">
+        <v>145.09</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Float: 50.0M</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="R3" t="n">
+        <v>163878384841</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>45845</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Extended Gap Down</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>291.37</v>
+      </c>
+      <c r="E4" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-975.24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Float: 50.0M</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>163286487976</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Extended Gap Down</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>310</v>
+      </c>
+      <c r="E5" t="n">
+        <v>322.27</v>
+      </c>
+      <c r="F5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-466.64</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>156.97</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Float: 50.0M</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="R5" t="n">
+        <v>161476647090</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -682,7 +883,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -702,7 +903,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +923,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1000.3</v>
+        <v>-3245.78</v>
       </c>
     </row>
     <row r="7">
@@ -742,7 +943,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1000.3</v>
+        <v>-811.4400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -787,17 +988,17 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Multi Day Breakout</t>
+          <t>Extended Gap Down</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>-1000.3</v>
+        <v>-3245.78</v>
       </c>
       <c r="D13" t="n">
-        <v>-1000.3</v>
+        <v>-811.4400000000001</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
